--- a/data/trans_dic/P1421-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1421-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,74</t>
+          <t>0,81; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,04</t>
+          <t>0,42; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,91</t>
+          <t>0,89; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,45</t>
+          <t>3,2; 6,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,65</t>
+          <t>1,33; 3,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,48</t>
+          <t>5,31; 9,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,41</t>
+          <t>3,15; 6,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,18</t>
+          <t>7,56; 11,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,85</t>
+          <t>1,36; 2,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,3</t>
+          <t>2,99; 5,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,34</t>
+          <t>2,35; 4,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,36</t>
+          <t>5,94; 8,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,69</t>
+          <t>1,57; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,82</t>
+          <t>0,53; 1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,79</t>
+          <t>0,48; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,59</t>
+          <t>2,69; 5,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,79</t>
+          <t>3,94; 6,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,29</t>
+          <t>3,56; 6,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,55</t>
+          <t>4,33; 7,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,26</t>
+          <t>8,17; 11,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,89</t>
+          <t>3,06; 4,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,7</t>
+          <t>2,19; 3,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,34</t>
+          <t>2,65; 4,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,26</t>
+          <t>5,85; 7,82</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,35</t>
+          <t>1,24; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,15</t>
+          <t>0,51; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,65</t>
+          <t>0,68; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,44</t>
+          <t>3,25; 6,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,69</t>
+          <t>5,04; 8,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,15</t>
+          <t>3,62; 7,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,49</t>
+          <t>3,5; 6,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,06</t>
+          <t>11,38; 15,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,75</t>
+          <t>3,43; 5,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,22</t>
+          <t>2,23; 4,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,15</t>
+          <t>2,41; 4,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,86</t>
+          <t>7,74; 10,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,37</t>
+          <t>2,11; 4,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,6</t>
+          <t>0,97; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,09</t>
+          <t>4,04; 7,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,77</t>
+          <t>6,33; 9,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,46</t>
+          <t>3,72; 6,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,8</t>
+          <t>4,61; 7,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,6</t>
+          <t>11,02; 14,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,8</t>
+          <t>4,69; 6,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,29</t>
+          <t>2,6; 4,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,02</t>
+          <t>3,11; 4,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,77</t>
+          <t>8,22; 10,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,0</t>
+          <t>1,95; 3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,63</t>
+          <t>0,88; 1,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,85</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,28</t>
+          <t>3,78; 5,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,65</t>
+          <t>4,98; 6,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,13</t>
+          <t>4,57; 6,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,37</t>
+          <t>4,69; 6,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,77</t>
+          <t>10,44; 12,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,59</t>
+          <t>3,64; 4,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,77</t>
+          <t>2,89; 3,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,04</t>
+          <t>3,06; 3,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,41</t>
+          <t>7,51; 8,66</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>67581</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>98526</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5185; 19027</t>
+          <t>5653; 19495</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3063; 14349</t>
+          <t>2958; 14133</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6148; 19668</t>
+          <t>6005; 21744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20780; 40981</t>
+          <t>22131; 43520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9921; 25107</t>
+          <t>9164; 26114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36247; 66070</t>
+          <t>37026; 65130</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22359; 43098</t>
+          <t>21192; 43723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52290; 75534</t>
+          <t>55411; 83196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17684; 39427</t>
+          <t>18834; 38426</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43081; 74162</t>
+          <t>41924; 73505</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32464; 58450</t>
+          <t>31731; 58729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78282; 109627</t>
+          <t>84485; 120191</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>103792</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>128931</t>
+          <t>143577</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15607; 35508</t>
+          <t>15090; 36771</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5261; 18572</t>
+          <t>5431; 19141</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4931; 18291</t>
+          <t>4861; 17413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16712; 54759</t>
+          <t>28201; 57210</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37291; 65752</t>
+          <t>38140; 65917</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36441; 64699</t>
+          <t>36606; 64148</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46980; 78745</t>
+          <t>45126; 77385</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77789; 107705</t>
+          <t>87392; 120571</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58585; 94311</t>
+          <t>59135; 95340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46594; 75663</t>
+          <t>44784; 75185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55498; 89607</t>
+          <t>54749; 89451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86343; 156158</t>
+          <t>123851; 165627</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96987</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>129756</t>
+          <t>145840</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7574; 22749</t>
+          <t>8392; 24295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3075; 16258</t>
+          <t>3840; 16857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5134; 20145</t>
+          <t>5173; 19811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22289; 45292</t>
+          <t>26026; 50186</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33897; 59395</t>
+          <t>34494; 59420</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28200; 55604</t>
+          <t>28108; 55389</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26630; 50932</t>
+          <t>27512; 51752</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54291; 131024</t>
+          <t>92191; 127352</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48225; 78329</t>
+          <t>46714; 78211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34841; 64769</t>
+          <t>34152; 65222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36888; 64125</t>
+          <t>37185; 65557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82921; 161129</t>
+          <t>124708; 165427</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>134418</t>
+          <t>141631</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>187484</t>
+          <t>194775</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20031; 41157</t>
+          <t>19915; 40845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9158; 24643</t>
+          <t>9163; 25619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8852; 24316</t>
+          <t>8805; 24241</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39617; 74841</t>
+          <t>39896; 74887</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67689; 101459</t>
+          <t>65753; 100851</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39529; 68005</t>
+          <t>39103; 66087</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48126; 81368</t>
+          <t>48116; 80918</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>108348; 159317</t>
+          <t>123123; 166329</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91635; 134747</t>
+          <t>92812; 134060</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52358; 85802</t>
+          <t>51933; 84452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61237; 99537</t>
+          <t>61550; 98681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>156875; 217140</t>
+          <t>172991; 222757</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62800; 98230</t>
+          <t>63733; 98843</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30012; 55803</t>
+          <t>30091; 56183</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35392; 62858</t>
+          <t>35615; 64238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115766; 182537</t>
+          <t>133411; 188991</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170511; 224671</t>
+          <t>168324; 222270</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>166549; 217776</t>
+          <t>162510; 218997</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>169038; 225855</t>
+          <t>166148; 223414</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>325032; 430155</t>
+          <t>389366; 457124</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>243028; 305286</t>
+          <t>241953; 304359</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202730; 263268</t>
+          <t>201953; 262877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211957; 280336</t>
+          <t>212211; 273862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>470235; 597952</t>
+          <t>545152; 628725</t>
         </is>
       </c>
     </row>
